--- a/data/attendance/AMPHI_عراس_2_ثانوي.xlsx
+++ b/data/attendance/AMPHI_عراس_2_ثانوي.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>عراس 2 ثانوي  |  AMPHI  |  2AS  |  عراس لمياء</t>
   </si>
@@ -43,6 +43,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -52,9 +55,6 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>27/09/2026</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -88,7 +88,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -596,7 +599,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -606,10 +609,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -651,13 +657,13 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>8</v>
@@ -753,7 +759,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -826,12 +832,17 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
